--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.22132815422476</v>
+        <v>2.960965825061524</v>
       </c>
       <c r="D2" t="n">
-        <v>26.95689394499751</v>
+        <v>4.380495266062097</v>
       </c>
       <c r="E2" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F2" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.38409358300001</v>
+        <v>5.912415207237502</v>
       </c>
       <c r="D3" t="n">
-        <v>38.83607394597603</v>
+        <v>6.310862016221106</v>
       </c>
       <c r="E3" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F3" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.47805097716372</v>
+        <v>7.877683283789104</v>
       </c>
       <c r="D4" t="n">
-        <v>45.06858240980877</v>
+        <v>7.323644641593925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F4" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.93221703393766</v>
+        <v>6.65148526801487</v>
       </c>
       <c r="D5" t="n">
-        <v>21.6390850083824</v>
+        <v>3.516351313862141</v>
       </c>
       <c r="E5" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F5" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.41978993324825</v>
+        <v>5.26821586415284</v>
       </c>
       <c r="D6" t="n">
-        <v>28.24395762250198</v>
+        <v>4.589643113656572</v>
       </c>
       <c r="E6" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F6" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.66670229393044</v>
+        <v>4.820839122763697</v>
       </c>
       <c r="D7" t="n">
-        <v>27.21212964837556</v>
+        <v>4.421971067861028</v>
       </c>
       <c r="E7" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F7" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.870184269235327</v>
+        <v>1.116404943750741</v>
       </c>
       <c r="D8" t="n">
-        <v>8.569293872381472</v>
+        <v>1.392510254261989</v>
       </c>
       <c r="E8" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F8" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.02924109761961</v>
+        <v>2.604751678363188</v>
       </c>
       <c r="D9" t="n">
-        <v>17.26046513344105</v>
+        <v>2.80482558418417</v>
       </c>
       <c r="E9" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F9" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.48431520690745</v>
+        <v>3.653701221122461</v>
       </c>
       <c r="D10" t="n">
-        <v>26.83211066460678</v>
+        <v>4.360217982998603</v>
       </c>
       <c r="E10" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F10" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.53189293015985</v>
+        <v>3.336432601150975</v>
       </c>
       <c r="D11" t="n">
-        <v>16.02363727556604</v>
+        <v>2.603841057279481</v>
       </c>
       <c r="E11" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F11" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.37656585372934</v>
+        <v>6.398691951231018</v>
       </c>
       <c r="D12" t="n">
-        <v>38.08248475868784</v>
+        <v>6.188403773286774</v>
       </c>
       <c r="E12" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F12" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.82330137919545</v>
+        <v>7.933786474119261</v>
       </c>
       <c r="D13" t="n">
-        <v>31.40587347756607</v>
+        <v>5.103454440104486</v>
       </c>
       <c r="E13" t="n">
-        <v>12.79630718817948</v>
+        <v>2.079399918079166</v>
       </c>
       <c r="F13" t="n">
-        <v>9.974187991584383</v>
+        <v>1.620805548632462</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
